--- a/04_Figures/extras/concordance_training/c_data/F04_source_data.xlsx
+++ b/04_Figures/extras/concordance_training/c_data/F04_source_data.xlsx
@@ -6121,151 +6121,151 @@
     <t xml:space="preserve">class</t>
   </si>
   <si>
+    <t xml:space="preserve">GOSLIM_AMINO_ACID_METABOLIC_PROCESS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GO Slim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concordant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOSLIM_CHROMOSOME_SEGREGATION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOSLIM_CILIUM_ORGANIZATION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOSLIM_CYTOKINESIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOSLIM_CYTOPLASMIC_TRANSLATION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOSLIM_DETOXIFICATION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOSLIM_DNA_RECOMBINATION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOSLIM_DNA_REPLICATION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOSLIM_ESTABLISHMENT_OR_MAINTENANCE_OF_CELL_POLARITY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOSLIM_EXTRACELLULAR_MATRIX_ORGANIZATION</t>
+  </si>
+  <si>
     <t xml:space="preserve">GOSLIM_GENERATION_OF_PRECURSOR_METABOLITES_AND_ENERGY</t>
   </si>
   <si>
-    <t xml:space="preserve">GO Slim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concordant</t>
+    <t xml:space="preserve">GOSLIM_GLYCOPROTEIN_METABOLIC_PROCESS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOSLIM_KETONE_METABOLIC_PROCESS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOSLIM_MICROTUBULE-BASED_MOVEMENT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOSLIM_MITOCHONDRION_ORGANIZATION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOSLIM_MITOTIC_NUCLEAR_DIVISION</t>
   </si>
   <si>
     <t xml:space="preserve">GOSLIM_MUSCLE_SYSTEM_PROCESS</t>
   </si>
   <si>
-    <t xml:space="preserve">GOSLIM_MITOCHONDRION_ORGANIZATION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GOSLIM_AMINO_ACID_METABOLIC_PROCESS</t>
+    <t xml:space="preserve">GOSLIM_NUCLEOCYTOPLASMIC_TRANSPORT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOSLIM_PROTEIN_FOLDING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOSLIM_PROTEIN_LOCALIZATION_TO_PLASMA_MEMBRANE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOSLIM_RIBOSOME_BIOGENESIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOSLIM_TELOMERE_ORGANIZATION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOSLIM_TRNA_METABOLIC_PROCESS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOSLIM_WOUND_HEALING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALLMARK_ADIPOGENESIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALLMARK_ALLOGRAFT_REJECTION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALLMARK_ANDROGEN_RESPONSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALLMARK_APICAL_JUNCTION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALLMARK_APOPTOSIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALLMARK_BILE_ACID_METABOLISM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALLMARK_COAGULATION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALLMARK_COMPLEMENT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALLMARK_DNA_REPAIR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALLMARK_E2F_TARGETS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALLMARK_EPITHELIAL_MESENCHYMAL_TRANSITION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALLMARK_ESTROGEN_RESPONSE_LATE</t>
   </si>
   <si>
     <t xml:space="preserve">HALLMARK_FATTY_ACID_METABOLISM</t>
   </si>
   <si>
+    <t xml:space="preserve">HALLMARK_G2M_CHECKPOINT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALLMARK_GLYCOLYSIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALLMARK_HEME_METABOLISM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALLMARK_HYPOXIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALLMARK_IL2_STAT5_SIGNALING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALLMARK_INTERFERON_GAMMA_RESPONSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALLMARK_MITOTIC_SPINDLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALLMARK_MTORC1_SIGNALING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALLMARK_MYC_TARGETS_V1</t>
+  </si>
+  <si>
     <t xml:space="preserve">HALLMARK_MYOGENESIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GOSLIM_CHROMOSOME_SEGREGATION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GOSLIM_CILIUM_ORGANIZATION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GOSLIM_CYTOKINESIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GOSLIM_CYTOPLASMIC_TRANSLATION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GOSLIM_DETOXIFICATION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GOSLIM_DNA_RECOMBINATION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GOSLIM_DNA_REPLICATION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GOSLIM_ESTABLISHMENT_OR_MAINTENANCE_OF_CELL_POLARITY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GOSLIM_EXTRACELLULAR_MATRIX_ORGANIZATION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GOSLIM_GLYCOPROTEIN_METABOLIC_PROCESS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GOSLIM_KETONE_METABOLIC_PROCESS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GOSLIM_MICROTUBULE-BASED_MOVEMENT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GOSLIM_MITOTIC_NUCLEAR_DIVISION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GOSLIM_NUCLEOCYTOPLASMIC_TRANSPORT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GOSLIM_PROTEIN_FOLDING</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GOSLIM_PROTEIN_LOCALIZATION_TO_PLASMA_MEMBRANE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GOSLIM_RIBOSOME_BIOGENESIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GOSLIM_TELOMERE_ORGANIZATION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GOSLIM_TRNA_METABOLIC_PROCESS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GOSLIM_WOUND_HEALING</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_ADIPOGENESIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_ALLOGRAFT_REJECTION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_ANDROGEN_RESPONSE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_APICAL_JUNCTION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_APOPTOSIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_BILE_ACID_METABOLISM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_COAGULATION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_COMPLEMENT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_DNA_REPAIR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_E2F_TARGETS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_EPITHELIAL_MESENCHYMAL_TRANSITION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_ESTROGEN_RESPONSE_LATE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_G2M_CHECKPOINT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_GLYCOLYSIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_HEME_METABOLISM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_HYPOXIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_IL2_STAT5_SIGNALING</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_INTERFERON_GAMMA_RESPONSE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_MITOTIC_SPINDLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_MTORC1_SIGNALING</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_MYC_TARGETS_V1</t>
   </si>
   <si>
     <t xml:space="preserve">HALLMARK_P53_PATHWAY</t>
@@ -58460,90 +58460,90 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1921</v>
+        <v>2033</v>
       </c>
       <c r="B2" t="s">
-        <v>1923</v>
+        <v>2034</v>
       </c>
       <c r="C2" t="n">
-        <v>2.97010681424908</v>
+        <v>1.85745173474227</v>
       </c>
       <c r="D2" t="n">
-        <v>1.92968494742863</v>
+        <v>1.12094750382066</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00000000000000000560397792703508</v>
+        <v>0.00319275442539914</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000813908863780655</v>
+        <v>0.6420564821638</v>
       </c>
       <c r="G2" t="n">
-        <v>151</v>
+        <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>152</v>
+        <v>95</v>
       </c>
       <c r="I2" t="n">
-        <v>151</v>
+        <v>95</v>
       </c>
       <c r="J2" t="n">
-        <v>1.8220878645431</v>
+        <v>1.35550286666421</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00292421588450552</v>
+        <v>0.308006998536021</v>
       </c>
       <c r="L2" t="n">
-        <v>2.97010681424908</v>
+        <v>1.85745173474227</v>
       </c>
       <c r="M2" t="n">
-        <v>1.92968494742863</v>
+        <v>1.12094750382066</v>
       </c>
       <c r="N2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" t="s">
-        <v>139</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>2033</v>
+        <v>2036</v>
       </c>
       <c r="B3" t="s">
         <v>2034</v>
       </c>
       <c r="C3" t="n">
-        <v>2.41825945468586</v>
+        <v>-0.826171658575519</v>
       </c>
       <c r="D3" t="n">
-        <v>1.63032567389698</v>
+        <v>1.05564664363655</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0000000000625153535221992</v>
+        <v>0.94083427169202</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00683335718915307</v>
+        <v>0.754414134624134</v>
       </c>
       <c r="G3" t="n">
-        <v>208</v>
+        <v>52</v>
       </c>
       <c r="H3" t="n">
-        <v>210</v>
+        <v>52</v>
       </c>
       <c r="I3" t="n">
-        <v>208</v>
+        <v>52</v>
       </c>
       <c r="J3" t="n">
-        <v>1.43029495141062</v>
+        <v>-1.12460245262448</v>
       </c>
       <c r="K3" t="n">
-        <v>0.103201674203791</v>
+        <v>0.691552078605185</v>
       </c>
       <c r="L3" t="n">
-        <v>2.41825945468586</v>
+        <v>-0.826171658575519</v>
       </c>
       <c r="M3" t="n">
-        <v>1.63032567389698</v>
+        <v>1.05564664363655</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
@@ -58554,90 +58554,90 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="B4" t="s">
         <v>2034</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.89378007007709</v>
+        <v>-1.17693000088112</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.955225472365153</v>
+        <v>1.55862536132802</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000169238459775695</v>
+        <v>0.552737414715102</v>
       </c>
       <c r="F4" t="n">
-        <v>0.907681433634004</v>
+        <v>0.181114313488071</v>
       </c>
       <c r="G4" t="n">
-        <v>160</v>
+        <v>31</v>
       </c>
       <c r="H4" t="n">
-        <v>160</v>
+        <v>31</v>
       </c>
       <c r="I4" t="n">
-        <v>160</v>
+        <v>31</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.63204379302582</v>
+        <v>-1.47705806139835</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0304218980792007</v>
+        <v>0.31164726989931</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.89378007007709</v>
+        <v>-1.17693000088112</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.955225472365153</v>
+        <v>1.55862536132802</v>
       </c>
       <c r="N4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="s">
-        <v>139</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="B5" t="s">
         <v>2034</v>
       </c>
       <c r="C5" t="n">
-        <v>2.02008190149362</v>
+        <v>-0.905825338243034</v>
       </c>
       <c r="D5" t="n">
-        <v>1.23379688827287</v>
+        <v>0.897690502394273</v>
       </c>
       <c r="E5" t="n">
-        <v>0.000180877231897007</v>
+        <v>0.857471512165075</v>
       </c>
       <c r="F5" t="n">
-        <v>0.439984689298347</v>
+        <v>0.918922114495776</v>
       </c>
       <c r="G5" t="n">
-        <v>121</v>
+        <v>37</v>
       </c>
       <c r="H5" t="n">
-        <v>121</v>
+        <v>37</v>
       </c>
       <c r="I5" t="n">
-        <v>121</v>
+        <v>37</v>
       </c>
       <c r="J5" t="n">
-        <v>1.48772993147192</v>
+        <v>-1.149058964951</v>
       </c>
       <c r="K5" t="n">
-        <v>0.122678813593458</v>
+        <v>0.677956804100776</v>
       </c>
       <c r="L5" t="n">
-        <v>2.02008190149362</v>
+        <v>-0.905825338243034</v>
       </c>
       <c r="M5" t="n">
-        <v>1.23379688827287</v>
+        <v>0.897690502394273</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -58648,43 +58648,43 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="B6" t="s">
         <v>2034</v>
       </c>
       <c r="C6" t="n">
-        <v>1.85745173474227</v>
+        <v>1.09585893999989</v>
       </c>
       <c r="D6" t="n">
-        <v>1.12094750382066</v>
+        <v>0.761268146919161</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00319275442539914</v>
+        <v>0.60427519315499</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6420564821638</v>
+        <v>0.999492568764001</v>
       </c>
       <c r="G6" t="n">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="H6" t="n">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="I6" t="n">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="J6" t="n">
-        <v>1.35550286666421</v>
+        <v>-0.890491540677686</v>
       </c>
       <c r="K6" t="n">
-        <v>0.308006998536021</v>
+        <v>0.920865879785131</v>
       </c>
       <c r="L6" t="n">
-        <v>1.85745173474227</v>
+        <v>1.09585893999989</v>
       </c>
       <c r="M6" t="n">
-        <v>1.12094750382066</v>
+        <v>0.761268146919161</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
@@ -58695,43 +58695,43 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="B7" t="s">
-        <v>1923</v>
+        <v>2034</v>
       </c>
       <c r="C7" t="n">
-        <v>1.82489931054386</v>
+        <v>0.935252182051207</v>
       </c>
       <c r="D7" t="n">
-        <v>1.31785129869172</v>
+        <v>-1.17110971802144</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00743412609951147</v>
+        <v>0.832004099091071</v>
       </c>
       <c r="F7" t="n">
-        <v>0.345172860132404</v>
+        <v>0.579903089462182</v>
       </c>
       <c r="G7" t="n">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="H7" t="n">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="I7" t="n">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="J7" t="n">
-        <v>1.08785310052012</v>
+        <v>1.12649423863166</v>
       </c>
       <c r="K7" t="n">
-        <v>0.702702319893865</v>
+        <v>0.679972486021124</v>
       </c>
       <c r="L7" t="n">
-        <v>1.82489931054386</v>
+        <v>0.935252182051207</v>
       </c>
       <c r="M7" t="n">
-        <v>1.31785129869172</v>
+        <v>-1.17110971802144</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -58742,43 +58742,43 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="B8" t="s">
-        <v>1923</v>
+        <v>2034</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.65841560350275</v>
+        <v>-0.928162225764295</v>
       </c>
       <c r="D8" t="n">
-        <v>0.827633933373506</v>
+        <v>0.79022906032464</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0415282556758717</v>
+        <v>0.830919462515331</v>
       </c>
       <c r="F8" t="n">
-        <v>0.971446962673331</v>
+        <v>0.9656524578953</v>
       </c>
       <c r="G8" t="n">
-        <v>94</v>
+        <v>25</v>
       </c>
       <c r="H8" t="n">
-        <v>94</v>
+        <v>25</v>
       </c>
       <c r="I8" t="n">
-        <v>94</v>
+        <v>25</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.55493664955157</v>
+        <v>-0.736632416821114</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0922459438088661</v>
+        <v>0.977758564958154</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.65841560350275</v>
+        <v>-0.928162225764295</v>
       </c>
       <c r="M8" t="n">
-        <v>0.827633933373506</v>
+        <v>0.79022906032464</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
@@ -58789,43 +58789,43 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="B9" t="s">
         <v>2034</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.826171658575519</v>
+        <v>-1.31863641524343</v>
       </c>
       <c r="D9" t="n">
-        <v>1.05564664363655</v>
+        <v>0.780491558540205</v>
       </c>
       <c r="E9" t="n">
-        <v>0.94083427169202</v>
+        <v>0.407077910500981</v>
       </c>
       <c r="F9" t="n">
-        <v>0.754414134624134</v>
+        <v>0.969911337986557</v>
       </c>
       <c r="G9" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="H9" t="n">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="I9" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.12460245262448</v>
+        <v>-1.3431924267127</v>
       </c>
       <c r="K9" t="n">
-        <v>0.691552078605185</v>
+        <v>0.471089165593245</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.826171658575519</v>
+        <v>-1.31863641524343</v>
       </c>
       <c r="M9" t="n">
-        <v>1.05564664363655</v>
+        <v>0.780491558540205</v>
       </c>
       <c r="N9" t="b">
         <v>0</v>
@@ -58836,43 +58836,43 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="B10" t="s">
         <v>2034</v>
       </c>
       <c r="C10" t="n">
-        <v>-1.17693000088112</v>
+        <v>-0.995532176574126</v>
       </c>
       <c r="D10" t="n">
-        <v>1.55862536132802</v>
+        <v>0.905993907395175</v>
       </c>
       <c r="E10" t="n">
-        <v>0.552737414715102</v>
+        <v>0.769657153126032</v>
       </c>
       <c r="F10" t="n">
-        <v>0.181114313488071</v>
+        <v>0.916912030127512</v>
       </c>
       <c r="G10" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H10" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I10" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.47705806139835</v>
+        <v>-1.25577630296143</v>
       </c>
       <c r="K10" t="n">
-        <v>0.31164726989931</v>
+        <v>0.568475214675529</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.17693000088112</v>
+        <v>-0.995532176574126</v>
       </c>
       <c r="M10" t="n">
-        <v>1.55862536132802</v>
+        <v>0.905993907395175</v>
       </c>
       <c r="N10" t="b">
         <v>0</v>
@@ -58883,43 +58883,43 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="B11" t="s">
         <v>2034</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.905825338243034</v>
+        <v>-0.700796497677842</v>
       </c>
       <c r="D11" t="n">
-        <v>0.897690502394273</v>
+        <v>1.30849421487627</v>
       </c>
       <c r="E11" t="n">
-        <v>0.857471512165075</v>
+        <v>0.980142256011022</v>
       </c>
       <c r="F11" t="n">
-        <v>0.918922114495776</v>
+        <v>0.509129050253359</v>
       </c>
       <c r="G11" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="H11" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="I11" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.149058964951</v>
+        <v>-1.31290602710404</v>
       </c>
       <c r="K11" t="n">
-        <v>0.677956804100776</v>
+        <v>0.558168908819133</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.905825338243034</v>
+        <v>-0.700796497677842</v>
       </c>
       <c r="M11" t="n">
-        <v>0.897690502394273</v>
+        <v>1.30849421487627</v>
       </c>
       <c r="N11" t="b">
         <v>0</v>
@@ -58930,43 +58930,43 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="B12" t="s">
         <v>2034</v>
       </c>
       <c r="C12" t="n">
-        <v>1.09585893999989</v>
+        <v>2.41825945468586</v>
       </c>
       <c r="D12" t="n">
-        <v>0.761268146919161</v>
+        <v>1.63032567389698</v>
       </c>
       <c r="E12" t="n">
-        <v>0.60427519315499</v>
+        <v>0.0000000000625153535221992</v>
       </c>
       <c r="F12" t="n">
-        <v>0.999492568764001</v>
+        <v>0.00683335718915307</v>
       </c>
       <c r="G12" t="n">
-        <v>116</v>
+        <v>208</v>
       </c>
       <c r="H12" t="n">
-        <v>116</v>
+        <v>210</v>
       </c>
       <c r="I12" t="n">
-        <v>116</v>
+        <v>208</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.890491540677686</v>
+        <v>1.43029495141062</v>
       </c>
       <c r="K12" t="n">
-        <v>0.920865879785131</v>
+        <v>0.103201674203791</v>
       </c>
       <c r="L12" t="n">
-        <v>1.09585893999989</v>
+        <v>2.41825945468586</v>
       </c>
       <c r="M12" t="n">
-        <v>0.761268146919161</v>
+        <v>1.63032567389698</v>
       </c>
       <c r="N12" t="b">
         <v>0</v>
@@ -58977,43 +58977,43 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="B13" t="s">
         <v>2034</v>
       </c>
       <c r="C13" t="n">
-        <v>0.935252182051207</v>
+        <v>-0.981843125047177</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.17110971802144</v>
+        <v>-1.33348386639528</v>
       </c>
       <c r="E13" t="n">
-        <v>0.832004099091071</v>
+        <v>0.779359796399542</v>
       </c>
       <c r="F13" t="n">
-        <v>0.579903089462182</v>
+        <v>0.450290927192426</v>
       </c>
       <c r="G13" t="n">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="H13" t="n">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="I13" t="n">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="J13" t="n">
-        <v>1.12649423863166</v>
+        <v>1.26702414399065</v>
       </c>
       <c r="K13" t="n">
-        <v>0.679972486021124</v>
+        <v>0.576858180092026</v>
       </c>
       <c r="L13" t="n">
-        <v>0.935252182051207</v>
+        <v>-0.981843125047177</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.17110971802144</v>
+        <v>-1.33348386639528</v>
       </c>
       <c r="N13" t="b">
         <v>0</v>
@@ -59024,43 +59024,43 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="B14" t="s">
         <v>2034</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.928162225764295</v>
+        <v>1.27144048452368</v>
       </c>
       <c r="D14" t="n">
-        <v>0.79022906032464</v>
+        <v>-0.918441924204581</v>
       </c>
       <c r="E14" t="n">
-        <v>0.830919462515331</v>
+        <v>0.420006402475624</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9656524578953</v>
+        <v>0.916912030127512</v>
       </c>
       <c r="G14" t="n">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="H14" t="n">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="I14" t="n">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.736632416821114</v>
+        <v>1.01769530703463</v>
       </c>
       <c r="K14" t="n">
-        <v>0.977758564958154</v>
+        <v>0.787421790816034</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.928162225764295</v>
+        <v>1.27144048452368</v>
       </c>
       <c r="M14" t="n">
-        <v>0.79022906032464</v>
+        <v>-0.918441924204581</v>
       </c>
       <c r="N14" t="b">
         <v>0</v>
@@ -59071,43 +59071,43 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="B15" t="s">
         <v>2034</v>
       </c>
       <c r="C15" t="n">
-        <v>-1.31863641524343</v>
+        <v>-1.27518040889157</v>
       </c>
       <c r="D15" t="n">
-        <v>0.780491558540205</v>
+        <v>-1.36041359318204</v>
       </c>
       <c r="E15" t="n">
-        <v>0.407077910500981</v>
+        <v>0.420006402475624</v>
       </c>
       <c r="F15" t="n">
-        <v>0.969911337986557</v>
+        <v>0.338251470870136</v>
       </c>
       <c r="G15" t="n">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="H15" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="I15" t="n">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.3431924267127</v>
+        <v>-0.781623819256255</v>
       </c>
       <c r="K15" t="n">
-        <v>0.471089165593245</v>
+        <v>0.977758564958154</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.31863641524343</v>
+        <v>-1.27518040889157</v>
       </c>
       <c r="M15" t="n">
-        <v>0.780491558540205</v>
+        <v>-1.36041359318204</v>
       </c>
       <c r="N15" t="b">
         <v>0</v>
@@ -59118,43 +59118,43 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="B16" t="s">
         <v>2034</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.995532176574126</v>
+        <v>2.02008190149362</v>
       </c>
       <c r="D16" t="n">
-        <v>0.905993907395175</v>
+        <v>1.23379688827287</v>
       </c>
       <c r="E16" t="n">
-        <v>0.769657153126032</v>
+        <v>0.000180877231897007</v>
       </c>
       <c r="F16" t="n">
-        <v>0.916912030127512</v>
+        <v>0.439984689298347</v>
       </c>
       <c r="G16" t="n">
-        <v>35</v>
+        <v>121</v>
       </c>
       <c r="H16" t="n">
-        <v>35</v>
+        <v>121</v>
       </c>
       <c r="I16" t="n">
-        <v>35</v>
+        <v>121</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.25577630296143</v>
+        <v>1.48772993147192</v>
       </c>
       <c r="K16" t="n">
-        <v>0.568475214675529</v>
+        <v>0.122678813593458</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.995532176574126</v>
+        <v>2.02008190149362</v>
       </c>
       <c r="M16" t="n">
-        <v>0.905993907395175</v>
+        <v>1.23379688827287</v>
       </c>
       <c r="N16" t="b">
         <v>0</v>
@@ -59165,43 +59165,43 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="B17" t="s">
         <v>2034</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.700796497677842</v>
+        <v>-1.02988161403635</v>
       </c>
       <c r="D17" t="n">
-        <v>1.30849421487627</v>
+        <v>1.07951632996022</v>
       </c>
       <c r="E17" t="n">
-        <v>0.980142256011022</v>
+        <v>0.728942660617127</v>
       </c>
       <c r="F17" t="n">
-        <v>0.509129050253359</v>
+        <v>0.738270265927533</v>
       </c>
       <c r="G17" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="H17" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="I17" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.31290602710404</v>
+        <v>-1.13488301410715</v>
       </c>
       <c r="K17" t="n">
-        <v>0.558168908819133</v>
+        <v>0.686754837582596</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.700796497677842</v>
+        <v>-1.02988161403635</v>
       </c>
       <c r="M17" t="n">
-        <v>1.30849421487627</v>
+        <v>1.07951632996022</v>
       </c>
       <c r="N17" t="b">
         <v>0</v>
@@ -59212,90 +59212,90 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="B18" t="s">
         <v>2034</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.981843125047177</v>
+        <v>-1.89378007007709</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.33348386639528</v>
+        <v>-0.955225472365153</v>
       </c>
       <c r="E18" t="n">
-        <v>0.779359796399542</v>
+        <v>0.000169238459775695</v>
       </c>
       <c r="F18" t="n">
-        <v>0.450290927192426</v>
+        <v>0.907681433634004</v>
       </c>
       <c r="G18" t="n">
-        <v>22</v>
+        <v>160</v>
       </c>
       <c r="H18" t="n">
-        <v>23</v>
+        <v>160</v>
       </c>
       <c r="I18" t="n">
-        <v>22</v>
+        <v>160</v>
       </c>
       <c r="J18" t="n">
-        <v>1.26702414399065</v>
+        <v>-1.63204379302582</v>
       </c>
       <c r="K18" t="n">
-        <v>0.576858180092026</v>
+        <v>0.0304218980792007</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.981843125047177</v>
+        <v>-1.89378007007709</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.33348386639528</v>
+        <v>-0.955225472365153</v>
       </c>
       <c r="N18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" t="s">
-        <v>2035</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="B19" t="s">
         <v>2034</v>
       </c>
       <c r="C19" t="n">
-        <v>1.27144048452368</v>
+        <v>-1.17346661394716</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.918441924204581</v>
+        <v>-0.698491397271011</v>
       </c>
       <c r="E19" t="n">
-        <v>0.420006402475624</v>
+        <v>0.540291223525501</v>
       </c>
       <c r="F19" t="n">
-        <v>0.916912030127512</v>
+        <v>0.999492568764001</v>
       </c>
       <c r="G19" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H19" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="I19" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J19" t="n">
-        <v>1.01769530703463</v>
+        <v>-0.917015587729752</v>
       </c>
       <c r="K19" t="n">
-        <v>0.787421790816034</v>
+        <v>0.879595305001022</v>
       </c>
       <c r="L19" t="n">
-        <v>1.27144048452368</v>
+        <v>-1.17346661394716</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.918441924204581</v>
+        <v>-0.698491397271011</v>
       </c>
       <c r="N19" t="b">
         <v>0</v>
@@ -59306,43 +59306,43 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="B20" t="s">
         <v>2034</v>
       </c>
       <c r="C20" t="n">
-        <v>-1.27518040889157</v>
+        <v>1.14672384767612</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.36041359318204</v>
+        <v>1.39194639923534</v>
       </c>
       <c r="E20" t="n">
-        <v>0.420006402475624</v>
+        <v>0.552737414715102</v>
       </c>
       <c r="F20" t="n">
-        <v>0.338251470870136</v>
+        <v>0.251956751953517</v>
       </c>
       <c r="G20" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="H20" t="n">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="I20" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.781623819256255</v>
+        <v>0.827181008408268</v>
       </c>
       <c r="K20" t="n">
-        <v>0.977758564958154</v>
+        <v>0.970184044431197</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.27518040889157</v>
+        <v>1.14672384767612</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.36041359318204</v>
+        <v>1.39194639923534</v>
       </c>
       <c r="N20" t="b">
         <v>0</v>
@@ -59353,43 +59353,43 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>2053</v>
+        <v>2054</v>
       </c>
       <c r="B21" t="s">
         <v>2034</v>
       </c>
       <c r="C21" t="n">
-        <v>-1.02988161403635</v>
+        <v>1.01945875650767</v>
       </c>
       <c r="D21" t="n">
-        <v>1.07951632996022</v>
+        <v>1.34325490131696</v>
       </c>
       <c r="E21" t="n">
-        <v>0.728942660617127</v>
+        <v>0.737143891839691</v>
       </c>
       <c r="F21" t="n">
-        <v>0.738270265927533</v>
+        <v>0.375424369377978</v>
       </c>
       <c r="G21" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="H21" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="I21" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.13488301410715</v>
+        <v>-0.792136396651876</v>
       </c>
       <c r="K21" t="n">
-        <v>0.686754837582596</v>
+        <v>0.970184044431197</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.02988161403635</v>
+        <v>1.01945875650767</v>
       </c>
       <c r="M21" t="n">
-        <v>1.07951632996022</v>
+        <v>1.34325490131696</v>
       </c>
       <c r="N21" t="b">
         <v>0</v>
@@ -59400,43 +59400,43 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="B22" t="s">
         <v>2034</v>
       </c>
       <c r="C22" t="n">
-        <v>-1.17346661394716</v>
+        <v>-0.769513285785038</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.698491397271011</v>
+        <v>-1.05124454351321</v>
       </c>
       <c r="E22" t="n">
-        <v>0.540291223525501</v>
+        <v>0.974871175175866</v>
       </c>
       <c r="F22" t="n">
-        <v>0.999492568764001</v>
+        <v>0.754099678456592</v>
       </c>
       <c r="G22" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H22" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="I22" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.917015587729752</v>
+        <v>0.860950084403115</v>
       </c>
       <c r="K22" t="n">
-        <v>0.879595305001022</v>
+        <v>0.934022451291021</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.17346661394716</v>
+        <v>-0.769513285785038</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.698491397271011</v>
+        <v>-1.05124454351321</v>
       </c>
       <c r="N22" t="b">
         <v>0</v>
@@ -59447,43 +59447,43 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="B23" t="s">
         <v>2034</v>
       </c>
       <c r="C23" t="n">
-        <v>1.14672384767612</v>
+        <v>-0.622171511206777</v>
       </c>
       <c r="D23" t="n">
-        <v>1.39194639923534</v>
+        <v>0.476786237684654</v>
       </c>
       <c r="E23" t="n">
-        <v>0.552737414715102</v>
+        <v>0.994188954851885</v>
       </c>
       <c r="F23" t="n">
-        <v>0.251956751953517</v>
+        <v>0.999492568764001</v>
       </c>
       <c r="G23" t="n">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="H23" t="n">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="I23" t="n">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="J23" t="n">
-        <v>0.827181008408268</v>
+        <v>0.66730614207324</v>
       </c>
       <c r="K23" t="n">
-        <v>0.970184044431197</v>
+        <v>0.991168501349497</v>
       </c>
       <c r="L23" t="n">
-        <v>1.14672384767612</v>
+        <v>-0.622171511206777</v>
       </c>
       <c r="M23" t="n">
-        <v>1.39194639923534</v>
+        <v>0.476786237684654</v>
       </c>
       <c r="N23" t="b">
         <v>0</v>
@@ -59494,43 +59494,43 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>2056</v>
+        <v>2057</v>
       </c>
       <c r="B24" t="s">
         <v>2034</v>
       </c>
       <c r="C24" t="n">
-        <v>1.01945875650767</v>
+        <v>0.896386563826968</v>
       </c>
       <c r="D24" t="n">
-        <v>1.34325490131696</v>
+        <v>1.17409843426276</v>
       </c>
       <c r="E24" t="n">
-        <v>0.737143891839691</v>
+        <v>0.868018255999955</v>
       </c>
       <c r="F24" t="n">
-        <v>0.375424369377978</v>
+        <v>0.608060972243445</v>
       </c>
       <c r="G24" t="n">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="H24" t="n">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="I24" t="n">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.792136396651876</v>
+        <v>-0.756302007788369</v>
       </c>
       <c r="K24" t="n">
-        <v>0.970184044431197</v>
+        <v>0.978040110208547</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01945875650767</v>
+        <v>0.896386563826968</v>
       </c>
       <c r="M24" t="n">
-        <v>1.34325490131696</v>
+        <v>1.17409843426276</v>
       </c>
       <c r="N24" t="b">
         <v>0</v>
@@ -59541,43 +59541,43 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>2057</v>
+        <v>2058</v>
       </c>
       <c r="B25" t="s">
         <v>2034</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.769513285785038</v>
+        <v>-1.26945819269398</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.05124454351321</v>
+        <v>0.90915191135564</v>
       </c>
       <c r="E25" t="n">
-        <v>0.974871175175866</v>
+        <v>0.421858094864759</v>
       </c>
       <c r="F25" t="n">
-        <v>0.754099678456592</v>
+        <v>0.918922114495776</v>
       </c>
       <c r="G25" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="H25" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="I25" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="J25" t="n">
-        <v>0.860950084403115</v>
+        <v>-1.30157992053225</v>
       </c>
       <c r="K25" t="n">
-        <v>0.934022451291021</v>
+        <v>0.491528771615981</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.769513285785038</v>
+        <v>-1.26945819269398</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.05124454351321</v>
+        <v>0.90915191135564</v>
       </c>
       <c r="N25" t="b">
         <v>0</v>
@@ -59588,43 +59588,43 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>2058</v>
+        <v>2059</v>
       </c>
       <c r="B26" t="s">
-        <v>2034</v>
+        <v>1923</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.622171511206777</v>
+        <v>1.54165458101299</v>
       </c>
       <c r="D26" t="n">
-        <v>0.476786237684654</v>
+        <v>1.01815612505309</v>
       </c>
       <c r="E26" t="n">
-        <v>0.994188954851885</v>
+        <v>0.0843101095720488</v>
       </c>
       <c r="F26" t="n">
-        <v>0.999492568764001</v>
+        <v>0.814258848548088</v>
       </c>
       <c r="G26" t="n">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="H26" t="n">
-        <v>32</v>
+        <v>96</v>
       </c>
       <c r="I26" t="n">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="J26" t="n">
-        <v>0.66730614207324</v>
+        <v>1.17462455130492</v>
       </c>
       <c r="K26" t="n">
-        <v>0.991168501349497</v>
+        <v>0.593876605223423</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.622171511206777</v>
+        <v>1.54165458101299</v>
       </c>
       <c r="M26" t="n">
-        <v>0.476786237684654</v>
+        <v>1.01815612505309</v>
       </c>
       <c r="N26" t="b">
         <v>0</v>
@@ -59635,43 +59635,43 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="B27" t="s">
-        <v>2034</v>
+        <v>1923</v>
       </c>
       <c r="C27" t="n">
-        <v>0.896386563826968</v>
+        <v>-0.894534284675131</v>
       </c>
       <c r="D27" t="n">
-        <v>1.17409843426276</v>
+        <v>0.546903357531042</v>
       </c>
       <c r="E27" t="n">
-        <v>0.868018255999955</v>
+        <v>0.858344846642719</v>
       </c>
       <c r="F27" t="n">
-        <v>0.608060972243445</v>
+        <v>0.999492568764001</v>
       </c>
       <c r="G27" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="H27" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="I27" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.756302007788369</v>
+        <v>-1.11197486218497</v>
       </c>
       <c r="K27" t="n">
-        <v>0.978040110208547</v>
+        <v>0.731626123923021</v>
       </c>
       <c r="L27" t="n">
-        <v>0.896386563826968</v>
+        <v>-0.894534284675131</v>
       </c>
       <c r="M27" t="n">
-        <v>1.17409843426276</v>
+        <v>0.546903357531042</v>
       </c>
       <c r="N27" t="b">
         <v>0</v>
@@ -59682,43 +59682,43 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>2060</v>
+        <v>2061</v>
       </c>
       <c r="B28" t="s">
-        <v>2034</v>
+        <v>1923</v>
       </c>
       <c r="C28" t="n">
-        <v>-1.26945819269398</v>
+        <v>-1.14855014030568</v>
       </c>
       <c r="D28" t="n">
-        <v>0.90915191135564</v>
+        <v>-1.06545252346788</v>
       </c>
       <c r="E28" t="n">
-        <v>0.421858094864759</v>
+        <v>0.606585234101178</v>
       </c>
       <c r="F28" t="n">
-        <v>0.918922114495776</v>
+        <v>0.754414134624134</v>
       </c>
       <c r="G28" t="n">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="H28" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="I28" t="n">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>-1.30157992053225</v>
+        <v>0.77727695445991</v>
       </c>
       <c r="K28" t="n">
-        <v>0.491528771615981</v>
+        <v>0.95851335539612</v>
       </c>
       <c r="L28" t="n">
-        <v>-1.26945819269398</v>
+        <v>-1.14855014030568</v>
       </c>
       <c r="M28" t="n">
-        <v>0.90915191135564</v>
+        <v>-1.06545252346788</v>
       </c>
       <c r="N28" t="b">
         <v>0</v>
@@ -59729,43 +59729,43 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>2061</v>
+        <v>2062</v>
       </c>
       <c r="B29" t="s">
         <v>1923</v>
       </c>
       <c r="C29" t="n">
-        <v>1.54165458101299</v>
+        <v>0.628746551724104</v>
       </c>
       <c r="D29" t="n">
-        <v>1.01815612505309</v>
+        <v>1.26397122312794</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0843101095720488</v>
+        <v>0.994188954851885</v>
       </c>
       <c r="F29" t="n">
-        <v>0.814258848548088</v>
+        <v>0.521838339424188</v>
       </c>
       <c r="G29" t="n">
-        <v>95</v>
+        <v>33</v>
       </c>
       <c r="H29" t="n">
-        <v>96</v>
+        <v>33</v>
       </c>
       <c r="I29" t="n">
-        <v>95</v>
+        <v>33</v>
       </c>
       <c r="J29" t="n">
-        <v>1.17462455130492</v>
+        <v>-1.0629654411354</v>
       </c>
       <c r="K29" t="n">
-        <v>0.593876605223423</v>
+        <v>0.756382358723331</v>
       </c>
       <c r="L29" t="n">
-        <v>1.54165458101299</v>
+        <v>0.628746551724104</v>
       </c>
       <c r="M29" t="n">
-        <v>1.01815612505309</v>
+        <v>1.26397122312794</v>
       </c>
       <c r="N29" t="b">
         <v>0</v>
@@ -59776,43 +59776,43 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>2062</v>
+        <v>2063</v>
       </c>
       <c r="B30" t="s">
         <v>1923</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.894534284675131</v>
+        <v>-0.897849748601819</v>
       </c>
       <c r="D30" t="n">
-        <v>0.546903357531042</v>
+        <v>-0.932121058500314</v>
       </c>
       <c r="E30" t="n">
-        <v>0.858344846642719</v>
+        <v>0.85730099784459</v>
       </c>
       <c r="F30" t="n">
-        <v>0.999492568764001</v>
+        <v>0.901905802108642</v>
       </c>
       <c r="G30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>-1.11197486218497</v>
+        <v>0.886324097264581</v>
       </c>
       <c r="K30" t="n">
-        <v>0.731626123923021</v>
+        <v>0.894384622726799</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.894534284675131</v>
+        <v>-0.897849748601819</v>
       </c>
       <c r="M30" t="n">
-        <v>0.546903357531042</v>
+        <v>-0.932121058500314</v>
       </c>
       <c r="N30" t="b">
         <v>0</v>
@@ -59823,43 +59823,43 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>2063</v>
+        <v>2064</v>
       </c>
       <c r="B31" t="s">
         <v>1923</v>
       </c>
       <c r="C31" t="n">
-        <v>-1.14855014030568</v>
+        <v>-1.06734912019188</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.06545252346788</v>
+        <v>0.957321681461487</v>
       </c>
       <c r="E31" t="n">
-        <v>0.606585234101178</v>
+        <v>0.70369408076175</v>
       </c>
       <c r="F31" t="n">
-        <v>0.754414134624134</v>
+        <v>0.881813056755809</v>
       </c>
       <c r="G31" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H31" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I31" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J31" t="n">
-        <v>0.77727695445991</v>
+        <v>-1.23333515137191</v>
       </c>
       <c r="K31" t="n">
-        <v>0.95851335539612</v>
+        <v>0.619717476327707</v>
       </c>
       <c r="L31" t="n">
-        <v>-1.14855014030568</v>
+        <v>-1.06734912019188</v>
       </c>
       <c r="M31" t="n">
-        <v>-1.06545252346788</v>
+        <v>0.957321681461487</v>
       </c>
       <c r="N31" t="b">
         <v>0</v>
@@ -59870,43 +59870,43 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>2064</v>
+        <v>2065</v>
       </c>
       <c r="B32" t="s">
         <v>1923</v>
       </c>
       <c r="C32" t="n">
-        <v>0.628746551724104</v>
+        <v>-0.729648688820858</v>
       </c>
       <c r="D32" t="n">
-        <v>1.26397122312794</v>
+        <v>1.3235681564112</v>
       </c>
       <c r="E32" t="n">
-        <v>0.994188954851885</v>
+        <v>0.96726691774569</v>
       </c>
       <c r="F32" t="n">
-        <v>0.521838339424188</v>
+        <v>0.504011762321694</v>
       </c>
       <c r="G32" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H32" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="I32" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="J32" t="n">
-        <v>-1.0629654411354</v>
+        <v>-1.08457406864617</v>
       </c>
       <c r="K32" t="n">
-        <v>0.756382358723331</v>
+        <v>0.754883294462256</v>
       </c>
       <c r="L32" t="n">
-        <v>0.628746551724104</v>
+        <v>-0.729648688820858</v>
       </c>
       <c r="M32" t="n">
-        <v>1.26397122312794</v>
+        <v>1.3235681564112</v>
       </c>
       <c r="N32" t="b">
         <v>0</v>
@@ -59917,43 +59917,43 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="B33" t="s">
         <v>1923</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.897849748601819</v>
+        <v>-1.18385284239006</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.932121058500314</v>
+        <v>0.812944267812262</v>
       </c>
       <c r="E33" t="n">
-        <v>0.85730099784459</v>
+        <v>0.552737414715102</v>
       </c>
       <c r="F33" t="n">
-        <v>0.901905802108642</v>
+        <v>0.956222415445981</v>
       </c>
       <c r="G33" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H33" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I33" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J33" t="n">
-        <v>0.886324097264581</v>
+        <v>-1.1706295559475</v>
       </c>
       <c r="K33" t="n">
-        <v>0.894384622726799</v>
+        <v>0.654902761999273</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.897849748601819</v>
+        <v>-1.18385284239006</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.932121058500314</v>
+        <v>0.812944267812262</v>
       </c>
       <c r="N33" t="b">
         <v>0</v>
@@ -59964,43 +59964,43 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>2066</v>
+        <v>2067</v>
       </c>
       <c r="B34" t="s">
         <v>1923</v>
       </c>
       <c r="C34" t="n">
-        <v>-1.06734912019188</v>
+        <v>-1.3718356962443</v>
       </c>
       <c r="D34" t="n">
-        <v>0.957321681461487</v>
+        <v>-1.77280899623212</v>
       </c>
       <c r="E34" t="n">
-        <v>0.70369408076175</v>
+        <v>0.37484414727166</v>
       </c>
       <c r="F34" t="n">
-        <v>0.881813056755809</v>
+        <v>0.072576925048265</v>
       </c>
       <c r="G34" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H34" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I34" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.23333515137191</v>
+        <v>0.67258298973099</v>
       </c>
       <c r="K34" t="n">
-        <v>0.619717476327707</v>
+        <v>0.989161671099496</v>
       </c>
       <c r="L34" t="n">
-        <v>-1.06734912019188</v>
+        <v>-1.3718356962443</v>
       </c>
       <c r="M34" t="n">
-        <v>0.957321681461487</v>
+        <v>-1.77280899623212</v>
       </c>
       <c r="N34" t="b">
         <v>0</v>
@@ -60011,43 +60011,43 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>2067</v>
+        <v>2068</v>
       </c>
       <c r="B35" t="s">
         <v>1923</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.729648688820858</v>
+        <v>-0.933564399527019</v>
       </c>
       <c r="D35" t="n">
-        <v>1.3235681564112</v>
+        <v>-0.845022967965958</v>
       </c>
       <c r="E35" t="n">
-        <v>0.96726691774569</v>
+        <v>0.826093526094235</v>
       </c>
       <c r="F35" t="n">
-        <v>0.504011762321694</v>
+        <v>0.946377802719846</v>
       </c>
       <c r="G35" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="H35" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="I35" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="J35" t="n">
-        <v>-1.08457406864617</v>
+        <v>0.917192329285479</v>
       </c>
       <c r="K35" t="n">
-        <v>0.754883294462256</v>
+        <v>0.867862893920574</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.729648688820858</v>
+        <v>-0.933564399527019</v>
       </c>
       <c r="M35" t="n">
-        <v>1.3235681564112</v>
+        <v>-0.845022967965958</v>
       </c>
       <c r="N35" t="b">
         <v>0</v>
@@ -60058,43 +60058,43 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>2068</v>
+        <v>2069</v>
       </c>
       <c r="B36" t="s">
         <v>1923</v>
       </c>
       <c r="C36" t="n">
-        <v>-1.18385284239006</v>
+        <v>-1.15491562146226</v>
       </c>
       <c r="D36" t="n">
-        <v>0.812944267812262</v>
+        <v>-0.636668501598411</v>
       </c>
       <c r="E36" t="n">
-        <v>0.552737414715102</v>
+        <v>0.581585551472067</v>
       </c>
       <c r="F36" t="n">
-        <v>0.956222415445981</v>
+        <v>0.999492568764001</v>
       </c>
       <c r="G36" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H36" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I36" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="J36" t="n">
-        <v>-1.1706295559475</v>
+        <v>-1.19730287663797</v>
       </c>
       <c r="K36" t="n">
-        <v>0.654902761999273</v>
+        <v>0.624176023876174</v>
       </c>
       <c r="L36" t="n">
-        <v>-1.18385284239006</v>
+        <v>-1.15491562146226</v>
       </c>
       <c r="M36" t="n">
-        <v>0.812944267812262</v>
+        <v>-0.636668501598411</v>
       </c>
       <c r="N36" t="b">
         <v>0</v>
@@ -60105,43 +60105,43 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>2069</v>
+        <v>1956</v>
       </c>
       <c r="B37" t="s">
         <v>1923</v>
       </c>
       <c r="C37" t="n">
-        <v>-1.3718356962443</v>
+        <v>-1.01368382321734</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.77280899623212</v>
+        <v>-1.28851352548776</v>
       </c>
       <c r="E37" t="n">
-        <v>0.37484414727166</v>
+        <v>0.754330568102876</v>
       </c>
       <c r="F37" t="n">
-        <v>0.072576925048265</v>
+        <v>0.53948578382691</v>
       </c>
       <c r="G37" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="H37" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I37" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>0.67258298973099</v>
+        <v>1.21085601807351</v>
       </c>
       <c r="K37" t="n">
-        <v>0.989161671099496</v>
+        <v>0.645919013881689</v>
       </c>
       <c r="L37" t="n">
-        <v>-1.3718356962443</v>
+        <v>-1.01368382321734</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.77280899623212</v>
+        <v>-1.28851352548776</v>
       </c>
       <c r="N37" t="b">
         <v>0</v>
@@ -60158,37 +60158,37 @@
         <v>1923</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.933564399527019</v>
+        <v>0.946192970334417</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.845022967965958</v>
+        <v>-1.10470304885824</v>
       </c>
       <c r="E38" t="n">
-        <v>0.826093526094235</v>
+        <v>0.81415420079349</v>
       </c>
       <c r="F38" t="n">
-        <v>0.946377802719846</v>
+        <v>0.698335865455959</v>
       </c>
       <c r="G38" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H38" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I38" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J38" t="n">
-        <v>0.917192329285479</v>
+        <v>0.975109923512627</v>
       </c>
       <c r="K38" t="n">
-        <v>0.867862893920574</v>
+        <v>0.826780211444555</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.933564399527019</v>
+        <v>0.946192970334417</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.845022967965958</v>
+        <v>-1.10470304885824</v>
       </c>
       <c r="N38" t="b">
         <v>0</v>
@@ -60205,37 +60205,37 @@
         <v>1923</v>
       </c>
       <c r="C39" t="n">
-        <v>-1.15491562146226</v>
+        <v>1.82489931054386</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.636668501598411</v>
+        <v>1.31785129869172</v>
       </c>
       <c r="E39" t="n">
-        <v>0.581585551472067</v>
+        <v>0.00743412609951147</v>
       </c>
       <c r="F39" t="n">
-        <v>0.999492568764001</v>
+        <v>0.345172860132404</v>
       </c>
       <c r="G39" t="n">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="H39" t="n">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="I39" t="n">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.19730287663797</v>
+        <v>1.08785310052012</v>
       </c>
       <c r="K39" t="n">
-        <v>0.624176023876174</v>
+        <v>0.702702319893865</v>
       </c>
       <c r="L39" t="n">
-        <v>-1.15491562146226</v>
+        <v>1.82489931054386</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.636668501598411</v>
+        <v>1.31785129869172</v>
       </c>
       <c r="N39" t="b">
         <v>0</v>
@@ -60246,43 +60246,43 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>1956</v>
+        <v>2072</v>
       </c>
       <c r="B40" t="s">
         <v>1923</v>
       </c>
       <c r="C40" t="n">
-        <v>-1.01368382321734</v>
+        <v>-1.71645739562688</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.28851352548776</v>
+        <v>-0.64878793474357</v>
       </c>
       <c r="E40" t="n">
-        <v>0.754330568102876</v>
+        <v>0.0978114621931295</v>
       </c>
       <c r="F40" t="n">
-        <v>0.53948578382691</v>
+        <v>0.999492568764001</v>
       </c>
       <c r="G40" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="H40" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="I40" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>1.21085601807351</v>
+        <v>-1.50492061466886</v>
       </c>
       <c r="K40" t="n">
-        <v>0.645919013881689</v>
+        <v>0.310058108549521</v>
       </c>
       <c r="L40" t="n">
-        <v>-1.01368382321734</v>
+        <v>-1.71645739562688</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.28851352548776</v>
+        <v>-0.64878793474357</v>
       </c>
       <c r="N40" t="b">
         <v>0</v>
@@ -60293,43 +60293,43 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>2072</v>
+        <v>2073</v>
       </c>
       <c r="B41" t="s">
         <v>1923</v>
       </c>
       <c r="C41" t="n">
-        <v>0.946192970334417</v>
+        <v>0.954321941595327</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.10470304885824</v>
+        <v>-0.710937921809155</v>
       </c>
       <c r="E41" t="n">
-        <v>0.81415420079349</v>
+        <v>0.819283347141674</v>
       </c>
       <c r="F41" t="n">
-        <v>0.698335865455959</v>
+        <v>0.999492568764001</v>
       </c>
       <c r="G41" t="n">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="H41" t="n">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="I41" t="n">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="J41" t="n">
-        <v>0.975109923512627</v>
+        <v>0.90838200767616</v>
       </c>
       <c r="K41" t="n">
-        <v>0.826780211444555</v>
+        <v>0.894012882197734</v>
       </c>
       <c r="L41" t="n">
-        <v>0.946192970334417</v>
+        <v>0.954321941595327</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.10470304885824</v>
+        <v>-0.710937921809155</v>
       </c>
       <c r="N41" t="b">
         <v>0</v>
@@ -60340,43 +60340,43 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>2073</v>
+        <v>2074</v>
       </c>
       <c r="B42" t="s">
         <v>1923</v>
       </c>
       <c r="C42" t="n">
-        <v>-1.71645739562688</v>
+        <v>-0.782806751874419</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.64878793474357</v>
+        <v>-2.04303983055551</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0978114621931295</v>
+        <v>0.969284666555382</v>
       </c>
       <c r="F42" t="n">
-        <v>0.999492568764001</v>
+        <v>0.00362024394240764</v>
       </c>
       <c r="G42" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="H42" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="I42" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="J42" t="n">
-        <v>-1.50492061466886</v>
+        <v>1.47621672959713</v>
       </c>
       <c r="K42" t="n">
-        <v>0.310058108549521</v>
+        <v>0.274991995985013</v>
       </c>
       <c r="L42" t="n">
-        <v>-1.71645739562688</v>
+        <v>-0.782806751874419</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.64878793474357</v>
+        <v>-2.04303983055551</v>
       </c>
       <c r="N42" t="b">
         <v>0</v>
@@ -60387,43 +60387,43 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>2074</v>
+        <v>2075</v>
       </c>
       <c r="B43" t="s">
         <v>1923</v>
       </c>
       <c r="C43" t="n">
-        <v>0.954321941595327</v>
+        <v>-0.700350689389167</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.710937921809155</v>
+        <v>-0.717089608242204</v>
       </c>
       <c r="E43" t="n">
-        <v>0.819283347141674</v>
+        <v>0.991184857774292</v>
       </c>
       <c r="F43" t="n">
         <v>0.999492568764001</v>
       </c>
       <c r="G43" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="H43" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="I43" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="J43" t="n">
-        <v>0.90838200767616</v>
+        <v>-0.729098104813617</v>
       </c>
       <c r="K43" t="n">
-        <v>0.894012882197734</v>
+        <v>0.98799545250393</v>
       </c>
       <c r="L43" t="n">
-        <v>0.954321941595327</v>
+        <v>-0.700350689389167</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.710937921809155</v>
+        <v>-0.717089608242204</v>
       </c>
       <c r="N43" t="b">
         <v>0</v>
@@ -60434,43 +60434,43 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>2075</v>
+        <v>2076</v>
       </c>
       <c r="B44" t="s">
         <v>1923</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.782806751874419</v>
+        <v>-1.59657829408821</v>
       </c>
       <c r="D44" t="n">
-        <v>-2.04303983055551</v>
+        <v>-0.878701773854117</v>
       </c>
       <c r="E44" t="n">
-        <v>0.969284666555382</v>
+        <v>0.195353918020972</v>
       </c>
       <c r="F44" t="n">
-        <v>0.00362024394240764</v>
+        <v>0.921206194997319</v>
       </c>
       <c r="G44" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="H44" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="I44" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>1.47621672959713</v>
+        <v>-1.61832541163054</v>
       </c>
       <c r="K44" t="n">
-        <v>0.274991995985013</v>
+        <v>0.228998675514868</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.782806751874419</v>
+        <v>-1.59657829408821</v>
       </c>
       <c r="M44" t="n">
-        <v>-2.04303983055551</v>
+        <v>-0.878701773854117</v>
       </c>
       <c r="N44" t="b">
         <v>0</v>
@@ -60481,43 +60481,43 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>2076</v>
+        <v>2077</v>
       </c>
       <c r="B45" t="s">
         <v>1923</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.700350689389167</v>
+        <v>-1.03002739930225</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.717089608242204</v>
+        <v>0.671075376521158</v>
       </c>
       <c r="E45" t="n">
-        <v>0.991184857774292</v>
+        <v>0.728942660617127</v>
       </c>
       <c r="F45" t="n">
-        <v>0.999492568764001</v>
+        <v>0.994446034801426</v>
       </c>
       <c r="G45" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="H45" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="I45" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.729098104813617</v>
+        <v>-0.964846839455004</v>
       </c>
       <c r="K45" t="n">
-        <v>0.98799545250393</v>
+        <v>0.83136732392146</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.700350689389167</v>
+        <v>-1.03002739930225</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.717089608242204</v>
+        <v>0.671075376521158</v>
       </c>
       <c r="N45" t="b">
         <v>0</v>
@@ -60528,43 +60528,43 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>2077</v>
+        <v>2078</v>
       </c>
       <c r="B46" t="s">
         <v>1923</v>
       </c>
       <c r="C46" t="n">
-        <v>-1.59657829408821</v>
+        <v>-1.33497380658543</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.878701773854117</v>
+        <v>1.06737074007666</v>
       </c>
       <c r="E46" t="n">
-        <v>0.195353918020972</v>
+        <v>0.384524505030834</v>
       </c>
       <c r="F46" t="n">
-        <v>0.921206194997319</v>
+        <v>0.751758141948878</v>
       </c>
       <c r="G46" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="H46" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="I46" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="J46" t="n">
-        <v>-1.61832541163054</v>
+        <v>-1.41570547282725</v>
       </c>
       <c r="K46" t="n">
-        <v>0.228998675514868</v>
+        <v>0.370105763517528</v>
       </c>
       <c r="L46" t="n">
-        <v>-1.59657829408821</v>
+        <v>-1.33497380658543</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.878701773854117</v>
+        <v>1.06737074007666</v>
       </c>
       <c r="N46" t="b">
         <v>0</v>
@@ -60575,43 +60575,43 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>2078</v>
+        <v>2079</v>
       </c>
       <c r="B47" t="s">
         <v>1923</v>
       </c>
       <c r="C47" t="n">
-        <v>-1.03002739930225</v>
+        <v>1.19924113429801</v>
       </c>
       <c r="D47" t="n">
-        <v>0.671075376521158</v>
+        <v>-1.3558148598397</v>
       </c>
       <c r="E47" t="n">
-        <v>0.728942660617127</v>
+        <v>0.46579077967454</v>
       </c>
       <c r="F47" t="n">
-        <v>0.994446034801426</v>
+        <v>0.268611799404971</v>
       </c>
       <c r="G47" t="n">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="H47" t="n">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="I47" t="n">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.964846839455004</v>
+        <v>1.44970895868957</v>
       </c>
       <c r="K47" t="n">
-        <v>0.83136732392146</v>
+        <v>0.228998675514868</v>
       </c>
       <c r="L47" t="n">
-        <v>-1.03002739930225</v>
+        <v>1.19924113429801</v>
       </c>
       <c r="M47" t="n">
-        <v>0.671075376521158</v>
+        <v>-1.3558148598397</v>
       </c>
       <c r="N47" t="b">
         <v>0</v>
@@ -60622,43 +60622,43 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>2079</v>
+        <v>2080</v>
       </c>
       <c r="B48" t="s">
         <v>1923</v>
       </c>
       <c r="C48" t="n">
-        <v>-1.33497380658543</v>
+        <v>0.951308057416725</v>
       </c>
       <c r="D48" t="n">
-        <v>1.06737074007666</v>
+        <v>-0.961351485152873</v>
       </c>
       <c r="E48" t="n">
-        <v>0.384524505030834</v>
+        <v>0.844137725468117</v>
       </c>
       <c r="F48" t="n">
-        <v>0.751758141948878</v>
+        <v>0.900259219983504</v>
       </c>
       <c r="G48" t="n">
-        <v>34</v>
+        <v>119</v>
       </c>
       <c r="H48" t="n">
-        <v>34</v>
+        <v>119</v>
       </c>
       <c r="I48" t="n">
-        <v>34</v>
+        <v>119</v>
       </c>
       <c r="J48" t="n">
-        <v>-1.41570547282725</v>
+        <v>0.800135032355511</v>
       </c>
       <c r="K48" t="n">
-        <v>0.370105763517528</v>
+        <v>0.989161671099496</v>
       </c>
       <c r="L48" t="n">
-        <v>-1.33497380658543</v>
+        <v>0.951308057416725</v>
       </c>
       <c r="M48" t="n">
-        <v>1.06737074007666</v>
+        <v>-0.961351485152873</v>
       </c>
       <c r="N48" t="b">
         <v>0</v>
@@ -60669,43 +60669,43 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>2080</v>
+        <v>2081</v>
       </c>
       <c r="B49" t="s">
         <v>1923</v>
       </c>
       <c r="C49" t="n">
-        <v>1.19924113429801</v>
+        <v>-1.65841560350275</v>
       </c>
       <c r="D49" t="n">
-        <v>-1.3558148598397</v>
+        <v>0.827633933373506</v>
       </c>
       <c r="E49" t="n">
-        <v>0.46579077967454</v>
+        <v>0.0415282556758717</v>
       </c>
       <c r="F49" t="n">
-        <v>0.268611799404971</v>
+        <v>0.971446962673331</v>
       </c>
       <c r="G49" t="n">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H49" t="n">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="I49" t="n">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J49" t="n">
-        <v>1.44970895868957</v>
+        <v>-1.55493664955157</v>
       </c>
       <c r="K49" t="n">
-        <v>0.228998675514868</v>
+        <v>0.0922459438088661</v>
       </c>
       <c r="L49" t="n">
-        <v>1.19924113429801</v>
+        <v>-1.65841560350275</v>
       </c>
       <c r="M49" t="n">
-        <v>-1.3558148598397</v>
+        <v>0.827633933373506</v>
       </c>
       <c r="N49" t="b">
         <v>0</v>
@@ -60716,49 +60716,49 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>2081</v>
+        <v>1921</v>
       </c>
       <c r="B50" t="s">
         <v>1923</v>
       </c>
       <c r="C50" t="n">
-        <v>0.951308057416725</v>
+        <v>2.97010681424908</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.961351485152873</v>
+        <v>1.92968494742863</v>
       </c>
       <c r="E50" t="n">
-        <v>0.844137725468117</v>
+        <v>0.00000000000000000560397792703508</v>
       </c>
       <c r="F50" t="n">
-        <v>0.900259219983504</v>
+        <v>0.000813908863780655</v>
       </c>
       <c r="G50" t="n">
-        <v>119</v>
+        <v>151</v>
       </c>
       <c r="H50" t="n">
-        <v>119</v>
+        <v>152</v>
       </c>
       <c r="I50" t="n">
-        <v>119</v>
+        <v>151</v>
       </c>
       <c r="J50" t="n">
-        <v>0.800135032355511</v>
+        <v>1.8220878645431</v>
       </c>
       <c r="K50" t="n">
-        <v>0.989161671099496</v>
+        <v>0.00292421588450552</v>
       </c>
       <c r="L50" t="n">
-        <v>0.951308057416725</v>
+        <v>2.97010681424908</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.961351485152873</v>
+        <v>1.92968494742863</v>
       </c>
       <c r="N50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O50" t="s">
-        <v>2035</v>
+        <v>139</v>
       </c>
     </row>
     <row r="51">
